--- a/downloads/[取得或處分資產公告]_整合總表.xlsx
+++ b/downloads/[取得或處分資產公告]_整合總表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,30 +466,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>7833 綠岩能源</t>
+          <t>1268 漢來美食</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>本公司董事會通過子公司利旺能源股份有限公司擬取得有價證券案</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+          <t>公告本公司一年內累積處分同一有價證券達實收資本額20%</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2330台灣積體電路製造股份有限公司</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>自民國115年4月14日至民國115年4月14日</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>交易數量：50,000股 每單位價格：新台幣2,015~2,035元 交易總金額：新台幣101,050千元</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>累積持有數量：普通股股數 10,000,000 股 累計投資金額：新台幣199,447,432元 持股比例：100% 權利受限情形：無受限情形</t>
+          <t>累計持有10,000股 累計持有17,600千元 累計持股比例0.000004% 質押：無</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>有價證券投資占總資產之比例：8.66% 有價證券投資占股東權益之比例：18.58% 營運資金：新台幣 -3,782,557元</t>
+          <t>占總資產比例：7.93%(含其他有價證券投資) 占股東權益比例：24.38%(含其他有價證券投資) 營運資金：-16,964千元</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>因應本公司經營國內太陽光電或其他再生能源發電設施，為平台發展策略考量。</t>
+          <t>實現投資獲利</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -501,30 +513,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>7911 阿波羅電力</t>
+          <t>1268 漢來美食</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>本公司公告一年內累積取得同一有價證券達實收資本額20%</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+          <t>公告本公司一年內累積取得同一有價證券達實收資本額20%</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2330台灣積體電路製造股份有限公司</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>自民國114年11月18日至民國115年4月28日</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>55,000股；新台幣1,390元~2,260元；新台幣96,633,531元</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>累積持有數量：為10,000,000股 累計投資金額：新台幣100,000,000元 持股比例：尚未確定。 權利受限情形：無受限情形。</t>
+          <t>累計持有30,000股；累計持有62,818,033元；累計持股比例0.0001%；質押：無</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>有價證券投資占總資產之比例：7.74% 有價證券投資占股東權益之比例：13.15% 營運資金：新台幣687,718,000元</t>
+          <t>占總資產比例：8.57%(含其他有價證券投資) 占股東權益比例：26.34%(含其他有價證券投資) 營運資金：-16,964千元 營運資金為負數，係應屬非流動資產之長期借款195,000元受限於銀行作業被列為流動資 產，營運資金實際上為正數。</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>營運規劃之資金需求。</t>
+          <t>投資理財</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -536,33 +560,1482 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>7911 阿波羅電力</t>
+          <t>3147 大綜</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>（更正）本公司公告一年內累積取得同一有價證券達實收資本額20%</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+          <t>本公司董事會決議參與認購國內壽險公司發行之次順位公司債</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>富邦人壽保險股份有限公司無擔保累積次順位普通公司債(甲券)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>自民國115年3月4日至民國115年3月4日</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>交易單位數量：1張 每單位價格：新台幣100,000,000元 交易總金額：新台幣100,000,000元</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>累積持有數量：為10,000,000股 累計投資金額：新台幣100,000,000元 持股比例：尚未確定。 權利受限情形：無受限情形。</t>
+          <t>交易單位數量：1張 每單位價格：新台幣100,000,000元 交易總金額：新台幣100,000,000元</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>有價證券投資占總資產之比例：7.74% 有價證券投資占股東權益之比例：13.15% 營運資金：新台幣687,718,000元</t>
+          <t>有價證券投資占總資產之比例：2.87% 有價證券投資占股東權益之比例：5.80% 營運資金：新台幣1095242仟元</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>營運規劃之資金需求。</t>
+          <t>提升資金運用效率</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
+        <is>
+          <t>公告本公司115年03月04日董事會通過認購國內壽險公司發行之次順位公司債</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>3163 波若威</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>一年內累積處分同一有價證券達本公司實收資本額20%以上</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>上詮光纖通信股份有限公司</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>自民國114年12月3日至民國115年4月17日</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>(1)交易數量：300,000 股 (2)每單位價格：新台幣618.49元 (3)交易總金額：新台幣185,547仟元</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>(1)累積持有本交易證券之數量：1,788,058 股 (2)累積持有本交易證券之金額：新台幣821,451仟元 (3)持股比例：1.5734% (4)質押：無</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>(1)佔總資產比例:23.13% (2)佔歸屬於母公司業主之權益比例:27.89% (3)營運資金數額(千元):1,938,868</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>資金運用</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3623 富晶通</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>公告本公司一年內累積處分同一有價證券達實收資本額20%</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2412中華電信</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>自民國114年8月5日至民國115年1月22日</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>交易數量:554,000股；每股平均價格約新台幣124.32元； 交易總金額:新台幣68,874仟元</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>持有餘額：256,000股 金額：新台幣31,826仟元 累積持股比例：0.003% 權利受限情形：無</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>占公司最近期財務報表中總資產比例：8.27% 占公司最近期財務報表中歸屬於母公司業主之權益之比例：10.81% 最近期財務報表中營運資金數額：新台幣231,159仟元</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>資金運用及資產配置</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>4138 曜亞</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>公告本公司一年內累積處分同一有價證券達實收資本額20%</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>KRX (214370.KQ) Caregen Co.,Ltd.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>自民國114年11月25日至民國115年1月23日</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>(1)交易數量：46,329 股 (2)每單位價格：韓元81,268.66元(折合新台幣1,757.12 元) (3)交易總金額：韓元3,765,096千元(折合新台幣 81,406千元)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>本公司累積持有本交易證券(含本次交易)之 (1)累積持有之數量：172,500股 (2)累積持有之金額：新台幣52,407千元 (3)持股比例：0.32% (4)質押情形：無</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>(1)占總資產之比例：35.78% (2)占歸屬母公司業主權益之比例：42.47% (3)最近期財務報表中營運資金數額：693,774仟元</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>確保投資效益</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>本公司出售該交易標的係已指定為透過其他綜合損益按公允價值衡量之金融資產</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>4735 豪展</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>公告本公司一年內累積處分同一有價證券達本公司實收資本額20%以上</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>(3595)山太士股份有限公司</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>自民國114年11月6日至民國115年3月26日</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>交易數量:90仟股，每單位價格:804，交易總金額:91,520仟元</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>累積持有本證券之數量:24仟股，累積持有本證券之金額:28,757仟元</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>佔最近財務報表(個體)中總資產之比例:7.74% 佔最近財務報表(合併)中歸屬於母公司業主之權益比例:9.19% 最近財務報表(個體)中營運資金數額:275,833仟元</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>財務投資</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>略</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>4735 豪展</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>(更正)公告本公司一年內累積處分同一有價證券達本公司實收資本額20%以上</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>(3595)山太士股份有限公司</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>自民國114年11月6日至民國115年3月26日</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>交易數量:90仟股，每單位價格:804，交易總金額:91,520仟元</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>累積持有本證券之數量:24仟股，累積持有本證券之金額:28,757仟元</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>佔最近財務報表(個體)中總資產之比例:7.74% 佔最近財務報表(合併)中歸屬於母公司業主之權益比例:9.19% 最近財務報表(個體)中營運資金數額:275,833仟元</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>財務投資</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>略</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>4735 豪展</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>(更正)公告本公司一年內累積處分同一有價證券達本公司實收資本額20%以上</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>(3595)山太士股份有限公司</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>自民國114年11月6日至民國115年3月26日</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>交易數量:90仟股，每單位價格:804，交易總金額:91,520仟元</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>累積持有本證券之數量:18仟股，累積持有本證券之金額:21,568仟元</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>佔最近財務報表(個體)中總資產之比例:7.74% 佔最近財務報表(合併)中歸屬於母公司業主之權益比例:9.19% 最近財務報表(個體)中營運資金數額:275,833仟元</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>財務投資</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>略</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>4735 豪展</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>(更正)公告本公司一年內累積處分同一有價證券達本公司實收資本額20%以上</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>(3595)山太士股份有限公司</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>自民國114年11月6日至民國115年3月26日</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>交易數量:90仟股，每單位價格:1017，交易總金額:91,520仟元</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>累積持有本證券之數量:18仟股，累積持有本證券之金額:21,568仟元</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>佔最近財務報表(個體)中總資產之比例:7.74% 佔最近財務報表(合併)中歸屬於母公司業主之權益比例:9.19% 最近財務報表(個體)中營運資金數額:275,833仟元</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>財務投資</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>略</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>4745 合富-KY</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>代重要子公司合富（香港）控股股份有限公司公告
+最近一年累積處分重要子公司合富中國有價證券達公告標準</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>合富(中國)醫療科技股份有限公司股權</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>自民國114年12月24日至民國114年12月31日</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>交易單位數量：3,980,000股 每單位價格：每單位平均價格為RMB 24.923 交易總金額：人民幣99,193,707元，約新台幣438,713,927元</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>累積持有本交易證券之數量：214,957,885股 累積持有本交易證券之金額：依合富中國12/31收盤價計算， 累積持有總金額為新台幣23,197,463.90元。 持股比例：54% 受限情形：無</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>占公司最近期財務報表中 總資產比例：6.60% 歸屬於母公司業主之權益之比例：17.06% 最近期財務報表中營運資金：3,606,029千元</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>因應當前市場競爭環境及業務發展需求， 藉由調整股權結構以提升集團營運效益與股東獲利</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1.本公司於2025年10月17日收到財團法人中華民國證券櫃檯買賣中心同意， 調整新增「處分對合富中國既有持股方式」降低對合富中國之股權至51%以上。 2.本公司於2025年11月21日董事會通過，子公司合富（香港）控股股份有限公司 擬規劃處分合富中國不超過 4%股權，並授權董事長全權負責並辦理相關事宜。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>5312 寶島科</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>公告本公司最近一年累積處分有價證券達公告標準</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>群聯電子股份有限公司</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>自民國114年3月7日至民國115年1月6日</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>交易數量:159,000股 每單位價格:平均962.85元 交易總金額:153,093,449元</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>數量:50,000股 金額:21,853,783元 持股比例:0.0242% 權利受限情形:無</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>占總資產比例:0.30% 占歸屬於母公司業主之權益比例:0.63% 營運資金數額:-267,485仟元</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>實現獲利</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>5315 光聯</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>公告本公司處分有價證券</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>富邦金融控股股份有限公司</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>自民國115年5月27日至民國115年5月28日</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>交易數量：2,018仟股。 每單位價格：平均每股新台幣109.51元。 交易總金額：新台幣220,998仟元。</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>迄目前為止持有數量：2,018,115股 迄目前為止持有金額：新台幣91,494,234元 迄目前為止持股比例： 0.014% 權利受限情形：無。</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>佔總資產比例:4.27%； 佔歸屬於母公司之業主權益比例:5.68%； 營運資金數額:新台幣-1,340,523仟元</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>財務投資與資產配置</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>5347 世界</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>本公司代子公司VIS Associates Inc.公告取得Natwest Markets plc.之普通公司債</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Natwest Markets plc.之普通公司債</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>自民國115年5月6日至民國115年5月6日</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>USG638RQG67：50,000單位；每單位US$100.674；總金額US$5佰萬元。 USG638G7P18：50,000單位；每單位US$102.821；總金額US$5佰萬元。</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>(1)數量:190,000單位 (2)金額:US$19佰萬元 (3)持股比例：不適用 (4)權利受限情形: 無</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>(1)有價證券投資(含本次交易)占公司最近期財務報表中總資產之比例： 5.68% (2)占公司最近期財務報表歸屬於母公司業主之權益之比例： 10.27% (3)最近期財報中營運資金（總資產減總負債）數額: 20,206,163千元</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>固定收益投資。</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>無。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>5432 新門</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>公告取得有價證券</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>群聯電子股份有限公司</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>自民國115年5月19日至民國115年5月19日</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>交易數量：55,000股 每股平均價格：新台幣2,525.45元 交易總金額：新台幣138,900仟元</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>數量：55,000股 金額：138,900仟元 持股比例：0.0252%</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>占總資產比例:32.418% 占母公司業主之權益比例:37.211% 營運資金:新台幣253,876仟元</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>為提高本公司之資金運用效益</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>6114 久威</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>公告本公司取得有價證券</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>台新新光辛特(2887I)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>自民國115年3月25日至民國115年3月26日</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>(1)交易數量(仟股):10,141 (2)平均每單位價格(元):9.40 (3)交易總金額(元):95,297,825</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>(1)累積持有本交易證券（含本次交易）：10,141仟股 (2)投資金額(含本次交易)：95,297,825元 (3)持股比例：0.33% (4)權利受限情形：無</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>(1)有價證券投資（含本次交易）占總資產之比例：4.25% (2)有價證券投資（含本次交易）占股東權益之比例：6.03% (3)營運資金：1,358,018仟元</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>提高本公司資金運用效益</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>6114 久威</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>公告本公司取得有價證券</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>台新新光辛特(2887I)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>自民國115年3月25日至民國115年3月26日</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>(1)交易數量(仟股):10,141 (2)平均每單位價格(元):9.40 (3)交易總金額(元):95,297,825</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>(1)累積持有本交易證券（含本次交易）：10,141仟股 (2)投資金額(含本次交易)：95,297,825元 (3)持股比例：0.33% (4)權利受限情形：無</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>(1)有價證券投資（含本次交易）占總資產之比例：4.25% (2)有價證券投資（含本次交易）占股東權益之比例：6.03% (3)營運資金：1,358,018仟元</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>提高本公司資金運用效益</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>6163 華電網</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>公告本公司一年內累積處分同一有價證券達實收資本額20%</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>芯原微電子(上海)股份有限公司</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>自民國114年3月17日至民國115年2月4日</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>562,548股； 平均單位價格人民幣124.603元(折合新台幣552.755元)； 交易總金額人民幣70,095仟元(折合新台幣310,951仟元)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>累計持有130,000股；累計持有132,138仟元；累計持股比例0.02%；質押：無</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>占總資產比例：2.83%(含其他有價證券投資) 占股東權益比例：6.51%(含其他有價證券投資) 營運資金：1,714,245仟元</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>實現投資獲利</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>6292 迅德</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>一年內累積出售同一有價證券達本公司實收資本額20%以上</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>凱基金</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>自民國114年5月23日至民國115年2月3日</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>交易數量:6,014仟股 每單位價格:17.89 交易總金額:107,619仟元</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>累積持本證券之數量:10,100仟股 累積持有證券之金額:160,720仟元</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>佔最近財務報表(個體)中總資產之比例:8% 佔最近財務報表(合併)中歸屬於母公司業主之權益比例:15% 最近財務報表(個體)中營運資金數額:275,003仟元</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>投資</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>6292 迅德</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>⼀年內累積處分同⼀有價證券達實收資本額20%以上</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>凱基⾦</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>自民國115年2月5日至民國115年2月11日</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>交易數量:7,548仟股 每單位價格:18.7625 交易總⾦額:141,620仟元</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>累積持有本證券之數量:10,100仟股 累積持有本證券之⾦額:160,720仟元</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>佔最近財務報表(個體)中總資產之⽐例:7.8% 佔最近財務報表(合併)中歸屬於⺟公司業主之權益⽐例:15.28% 最近財務報表(個體)中營運資⾦數額:275,003仟元</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>⺒達預期的投資效益,故處分之。</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>無。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>6419 京晨科</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>公告本公司最近一年累積處分有價證券達公告標準</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Berkshire Hathaway Inc. Class A</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>自民國115年3月9日至民國115年3月9日</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Berkshire Hathaway Inc. Class A: 交易數量:3股 每單位價格:美金739,958.305元 交易總金額:美金 2,219,874.915元</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>已無持有本交易證券</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>占總資產比例:65.48% 占歸屬於母公司業主之權益比例:115.30% 營運資金數額:292,553仟元</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>投資組合</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>6419 京晨科</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>代子公司感動智慧科技股份有限公司公告
+最近一年累積取得有價證券達公告標準</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>台灣積體電路製造股份有限公司</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>自民國115年3月27日至民國115年5月18日</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>台灣積體電路製造股份有限公司 交易數量:34.45千股 每單位價格:新台幣 2,061.06元 交易總金額:新台幣 71,004千元</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>本公司 持有餘額:台灣積體電路製造股份有限公司 245千股 金額:新台幣 548,800千元 持股比例:0.0009% 權利受限情形:質押122千股 子公司-感動智慧科技股份有限公司 持有餘額:台灣積體電路製造股份有限公司 34.45千股 金額:新台幣 77,168千元 持股比例:0.0001% 權利受限情形:無</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>占總資產比例:11.94% 占歸屬於母公司業主之權益比例:16.90% 營運資金數額:320,889仟元</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>投資組合</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>6419 京晨科</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>代子公司感動智慧科技股份有限公司公告
+最近一年累積取得有價證券達公告標準</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>台灣積體電路製造股份有限公司</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>自民國115年5月19日至民國115年5月19日</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>台灣積體電路製造股份有限公司 交易數量:13.55千股 每單位價格:新台幣 2,210.20元 交易總金額:新台幣 29,948千元</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>本公司 持有餘額:台灣積體電路製造股份有限公司 245千股 金額:新台幣 540,225千元 持股比例:0.0009% 權利受限情形:質押122千股 子公司-感動智慧科技股份有限公司 持有餘額:台灣積體電路製造股份有限公司 48千股 金額:新台幣 105,840千元 持股比例:0.0002% 權利受限情形:無</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>占總資產比例:16.37% 占歸屬於母公司業主之權益比例:23.18% 營運資金數額:320,889仟元</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>投資組合</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>6574 霈方</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>公告本公司最近一年累積取得有價證券達公告標準</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>台灣積體電路製造股份有限公司</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>自民國114年10月17日至民國115年2月2日</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>交易數量：45仟股 每股平均價格：新台幣1,573元 交易總金額：新台幣70,785,000元</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>持有數量：45仟股 金額：新台幣70,785,000元 持股比例：0.00% 權利受限情形：無</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>佔總資產比例：8.72% 佔歸屬於母公司業主之權益比例：9.23% 營運資金數額：384,163仟元</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>投資組合</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>6574 霈方</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>公告本公司最近一年累積取得有價證券達公告標準</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>台灣積體電路製造股份有限公司</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>自民國115年2月3日至民國115年2月3日</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>交易數量：38仟股 每股平均價格：新台幣1,796.0526元 交易總金額：新台幣68,250,000元</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>持有數量：83仟股 金額：新台幣139,035,000元 持股比例：0.00% 權利受限情形：無</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>佔總資產比例：33.53% 佔歸屬於母公司業主之權益比例：35.48% 營運資金數額：384,163仟元</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>投資組合</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>6574 霈方</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>補充說明本公司取得有價證券投資計畫</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>台灣積體電路製造股份有限公司</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>自民國114年10月17日至民國115年2月3日</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>交易數量：不適用 每股平均價格：不適用 交易總金額：預計交易新台幣142,000,000元</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>持有數量：83仟股 金額：新台幣139,035,000元 持股比例：0.00% 權利受限情形：無</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>佔總資產比例：33.53% 佔歸屬於母公司業主之權益比例：35.48% 營運資金數額：384,163仟元</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>投資組合</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>本公司於民國115年2月2日經董事長核決，規劃取得台積電股票之投資金額 以新台幣1.42億元為上限，其中已包含114年度已取得金額新台幣40,865,000元。 截至目前止，本公司累計已取得金額為新台幣139,035,000元， 與原規劃投資上限差額新台幣2,965,000元，後續將不再執行取得。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>6597 立誠</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>公告本公司最近一年累積取得有價證券達公告標準</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>(8299)群聯電子股份有限公司</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>自民國115年3月5日至民國115年4月30日</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>交易數量43,000股、每股平均價格1931.63元及交易總金額83,060,284元</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>迄115/04/30止，累積持有群聯之數量23,000股、金額46,344,687元、 持股比例0.0106%，無權利受限情形。</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>占總資產比例:6.54% 占歸屬於母公司業主之權益比例:10.22% 營運資金數額: 238,782仟元</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>財務性投資</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>6597 立誠</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>公告本公司最近一年累積處分有價證券達公告標準</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>(8299)群聯電子股份有限公司</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>自民國115年3月16日至民國115年5月6日</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>交易數量43,000股、每股平均價格2129.31元及交易總金額91,560,330元</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>(1)群聯(8299)：無 (2)權利受限情形：無</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>占總資產比例:7.21% 占歸屬於母公司業主之權益比例:11.27% 營運資金數額: 238,782仟元</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>財務性投資</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>6679 鈺太</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>公告本公司取得有價證券</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>文曄科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>自民國115年4月30日至民國115年5月6日</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>交易數量 ：750,000股 每單位價格：新台幣210.45元 交易總金額：新台幣157,835,964元</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>累積持有數量：8,170,000股 累積持有金額：新台幣1,772,890,000元(依115年第1季評價資料) 累積持有持股比例：0.65% 權利受限情形：質押0股</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>占公司最近期財務報表中總資產之比例:43.42% 占歸屬於母公司業主之權益比例:41.64% 最近期財務報表中營運資金數額：新台幣3,459,114,550元</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>財務投資</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>4749 新應材</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>公告本公司決議取得私募有價證券</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>累積持有數量: 8,500張 累積持有金額：新台幣306,000,000元 持股比例：不適用 權利受限情形：無</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>占總資產比例：2.81% 占業主權益比例：3.42% 營運資金數額：新台幣 3,890,444 仟元</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>經營策略規劃</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>5299 杰力</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>公告本公司參與認購富邦人壽保險股份有限公司一一五年度
+第一期無擔保次順位普通公司債</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>累計持有本交易證券： 數量：170張 累計總金額新台幣為170,280,000元</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>佔總資產比例：4.5% 佔業主權益比例：5.22% 營運資金數額：NT$1,477,188仟元</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>固定收益投資。</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>無。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>8032 光菱</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>公告本公司董事會決議取得有價證券</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>金額:上限190,200,000元(600萬美元以4/14匯率31.7計算) 權利受限情形(如質押情形):無</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>(1)占公司最近期財務報表中總資產之比例：5.72% (2)占公司最近期財務報表中股東權益之比例：8.56% (3)公司最近期財務報表中營運資金數額：377,560 仟元</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>切入新能源市場，尋求新業務拓展機會與營收挹注</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>8032 光菱</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>公告本公司董事會決議取得有價證券(更正)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>(1)金額:上限190,200,000元(600萬美元以4/14匯率31.7計算) (2)權利受限情形(如質押情形):無</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>(1)占公司最近期財務報表中總資產之比例：5.72% (2)占公司最近期財務報表中股東權益之比例：8.56% (3)公司最近期財務報表中營運資金數額：377,560 仟元</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>切入新能源市場，尋求新業務拓展機會與營收挹注</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>8171 天宇</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>代子公司昆山萬金天宇貿易有限公司公告累計取得及處份
+有價證券達公告標準</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>餘額:人民幣7,000,000元(約當新台幣 31,976,000 元)，無質押情形</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>占母公司最近期個體財務報表總資產比例：1.17% 占最近期合併財務報表歸屬於母公司業主之權益比例：1.66% 母公司最近期個體財務報表中營運資金數額：596,010仟元</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>投資穩定收益型標的</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>8435 鉅邁</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>公告本公司取得有價證券</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>累積數量:8,400,000股 金額:新台幣285,600,000元 持股比例:70% 權利受限情形:無</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>占公司最近期財務報表中總資產之比例:93.07% 占公司最近期財務報表中業主權益之比例:120.39% 最近期財務報表中營運資金數額:459,167仟元</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>長期股權投資</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
         <is>
           <t>無</t>
         </is>
